--- a/artfynd/A 6454-2022 artfynd.xlsx
+++ b/artfynd/A 6454-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6454-2022 artfynd.xlsx
+++ b/artfynd/A 6454-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104374021</v>
+        <v>104374516</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318561.2127517399</v>
+        <v>318991</v>
       </c>
       <c r="R2" t="n">
-        <v>6553746.351832784</v>
+        <v>6553739</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2022-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +763,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bärbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Kolad stubbe # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,37 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104374516</v>
+        <v>104374021</v>
       </c>
       <c r="B3" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318990.8884731251</v>
+        <v>318561</v>
       </c>
       <c r="R3" t="n">
-        <v>6553738.849789678</v>
+        <v>6553746</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,19 +867,9 @@
           <t>2022-10-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,22 +884,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Bärbarrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Kolad stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 6454-2022 artfynd.xlsx
+++ b/artfynd/A 6454-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104374516</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104374021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>